--- a/data/daily/2026-10/2026-10-07.xlsx
+++ b/data/daily/2026-10/2026-10-07.xlsx
@@ -11,7 +11,9 @@
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="다이소몰" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="다이소몰_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="올리브영" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="올리브영_카드형" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="카테고리통계" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1193,14 +1195,114 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1215,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1240,160 +1342,60 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="323850" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1448,9 +1450,264 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="866775" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1468,12 +1725,267 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1498,7 +2010,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1523,7 +2035,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1548,7 +2060,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1573,7 +2085,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1598,7 +2110,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1623,7 +2135,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1648,7 +2160,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2084,23 +2596,19 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16227</v>
+        <v>16228</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>피로 회복과 활력 — 지치고 피로할 때 섭취 시 에너지가 충전되고 활력이 솟아나는 효과가 있음</t>
+          <t>탁월한 피로 회복 — 지치고 피로할 때 먹으면 힘이 나고 활력이 돋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용으로 제격 — 패키지가 고급스러우며 받는 사람과 주는 사람 모두의 만족도가 매우 높음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>우수한 맛과 제형 — 액상과 알약 형태로 구성되어 맛이 좋고 부담 없이 든든하게 복용 가능함</t>
-        </is>
-      </c>
+          <t>편리한 섭취 방식 — 액상과 알약 형태로 섭취가 쉬우며 맛이 좋아 에너지를 충전하기 좋음</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2147,17 +2655,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>피로 개선과 활력 — 학업이나 업무로 지치고 피곤할 때 먹으면 에너지가 충전되는 느낌을 받음</t>
+          <t>확실한 활력 충전 — 과중한 업무나 학업으로 지쳤을 때 복용하면 빠른 피로 완화에 도움을 줌</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>편리한 휴대성 — 한 손에 들어오는 콤팩트한 크기에 액상과 알약이 함께 있어 외출 시 챙기기 편함</t>
+          <t>우수한 휴대 편의 — 알약과 액상이 콤팩트한 한 포에 같이 있어 외출이나 여행 시 챙기기 편함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>높은 선물 만족도 — 포장이 깔끔하고 배송이 빨라 지인들에게 센스 있는 선물로 추천할 만함</t>
+          <t>센스 있는 패키지 — 포장이 무척 깔끔하고 고급스러워 주변 지인들에게 선물용으로 기분 좋게 전달 가능함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2206,18 +2714,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 피로 완화 — 복용한 다음 날 피로감이 덜하고 힘들 때 신속하게 에너지를 채워줌</t>
+          <t>기력 보충에 효과 — 환절기에 기운을 차릴 수 있게 돕고 힘들 때 일시적인 피로 회복 효과가 있음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>기분 좋은 선물 — 직접 구매하기엔 다소 부담스러운 가격의 인기 제품을 선물로 받아 만족도가 높음</t>
+          <t>높은 선물 선호도 — 다소 고가의 영양제라 직접 구매하기보다 선물로 받았을 때 만족도가 무척 높음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>선물 발송자 미표기 — 보낸 사람이 누구인지 기재되어 있지 않고 관련 문의 시 고객센터의 답변이 모호함</t>
+          <t>보낸이 확인 불가 — 선물 보낸 사람이 누구인지 표시되지 않고 관련 문의에 불분명하게 답변함</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2265,17 +2773,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 식감 — 쫄깃하고 달콤한 젤리 제형으로 영양제 느낌 없이 간식처럼 맛있게 먹을 수 있음</t>
+          <t>맛있는 젤리 제형 — 새콤달콤하고 맛과 향이 훌륭하여 간식처럼 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 섭취 방식 — 알약을 잘 삼키지 못하거나 수술 후 목넘김이 힘든 사람도 편하게 씹어서 섭취함</t>
+          <t>편리한 목넘김 — 알약을 잘 넘기지 못하거나 수술 후 삼키기 어려운 분들도 쉽게 씹어서 섭취 가능함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>귀여운 패키지 디자인 — 감귤 모양의 케이스 디자인과 동봉된 키캡 등의 구성품이 무척 귀여움</t>
+          <t>아기자기한 부자재 — 손잡이가 달린 귀여운 감귤 패키지와 소장 가치 있는 키캡 사은품이 동봉됨</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2313,7 +2821,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928130637_4b5e189e4cc74b40bc33bd3c75d10253.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261006173014_9a46de80b829480796c23d0cd4a75de9.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -2324,18 +2832,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>우수한 휴대와 복용 — 바쁜 출근길에 가볍게 하나씩 챙겨 나갈 수 있고 마시는 형태라 복용이 편리함</t>
+          <t>우수한 휴대성 — 출근길에 가볍게 챙겨 나갈 수 있는 개별 스틱 패키지로 휴대와 보관이 편함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>효과적인 피로 개선 — 피로 완화와 활력 충전에 뛰어나며 환절기 건강 관리용으로 추천함</t>
+          <t>간편한 섭취 방식 — 마시는 올인원 형태로 설계되어 삼키기 부드럽고 덜 피곤한 효과를 체감함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>배송 포장의 아쉬움 — 전용 쇼핑백이 누락되고 별도의 보완 포장 없이 택배 상자에 본품만 배송되어 당황스러움</t>
+          <t>아쉬운 배송 포장 — 타 쇼핑몰과 달리 쇼핑백이나 고정용 완충 없이 일반 박스에 그냥 배송되어 아쉬움</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2379,22 +2887,22 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8741</v>
+        <v>8742</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 — 자기 전에 먹으면 아침에 기상할 때 몸이 무겁지 않고 피로 해소에 확실히 도움됨</t>
+          <t>개선되는 아침 피로 — 취침 전 복용 시 다음 날 아침 일어날 때 몸 상태가 가볍게 느껴짐</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>알찬 패키지 구성 — 선물하기 단독 에디션으로 추가 증정분이 포함되어 알차고 깔끔한 첫인상을 줌</t>
+          <t>실속 있는 패키지 — 7입 본품에 2입을 추가 증정하는 알찬 패키지 구성으로 선물 전달용에 적합함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>다소 빈약한 부피감 — 소포장 제품 특성상 직접 보았을 때 선물로서 풍성해 보이는 느낌은 덜함</t>
+          <t>부족해 보이는 볼륨 — 소포장 위주로 디자인되어 제품 수령 시 겉으로 풍성해 보이지 않을 수 있음</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2442,12 +2950,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 고급스러운 박스와 종이가방이 동봉되어 격식 있는 명절 선물용으로 매우 훌륭함</t>
+          <t>고품격 패키징 — 포장 외형이 매우 단정하고 예쁘며 종이가방이 기본 제공되어 품격 있는 선물로 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>면역력 및 활력 충전 — 피로를 빠르게 해결해주고 환절기 감기 예방 및 면역력을 키우는 데 탁월함</t>
+          <t>즉각적인 체력 개선 — 피로에 지쳤을 때 복용 즉시 에너지가 생겨 기운을 차릴 수 있게 도움을 줌</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -2458,7 +2966,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2466,48 +2974,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>39,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>780</v>
+        <v>1743</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>성별 맞춤형 선택 옵션 — 남성과 여성을 위한 포뮬러가 따로 설계 및 구분되어 있어 성별에 맞춰 선물하기 좋음</t>
+          <t>혁신적인 특수 마개 — 빛과 습기에 예민한 분말과 액상을 분리 밀폐하는 4중 구조 프레스 캡을 사용하여 안전함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>거부감 없는 맛과 제형 — 비타민 특유의 거북하고 쓴맛이 없어 복용하기에 부담감이 없고 섭취가 편리함</t>
+          <t>매우 빠른 총알 배송 — 선물 배송지 입력 후 만 하루 만에 받아볼 수 있을 만큼 무척 신속함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>풍부한 영양 성분 — 기존 이뮨 라인보다 함유된 영양소가 더 많아 피로 회복에 탁월한 효과가 있음</t>
+          <t>부담 없는 가격대 — 고급스러운 외관 대비 가격 부담이 적어 출산 선물이나 연령대 있는 생일 선물용에 좋음</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -2517,7 +3025,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2525,50 +3033,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39,000원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12159594</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>1742</v>
+        <v>780</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>혁신적인 밀폐 용기 — 프레스버튼캡 구조로 빛과 습기에 약한 분말 원료를 상하지 않게 완벽히 보관함</t>
+          <t>성별 맞춤 선택 — 남성과 여성을 위한 최적화 영양이 다르게 설계되어 맞춤형 관리가 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>만족스러운 맛과 영양 — 맛과 영양을 모두 잡았으며 음주나 육아 등으로 지친 몸의 피로감을 확실히 덜어줌</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>품격 있는 가성비 선물 — 패키지가 은근히 묵직하고 고급스러워 받는 사람에게 기분 좋은 가성비 선물이 됨</t>
-        </is>
-      </c>
+          <t>우수한 목넘김 — 영양제 고유의 불쾌한 쓴맛이나 냄새가 적어 진득하고 건강하게 섭취하기 좋음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -2615,23 +3119,23 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>신뢰도 높은 원산지 — 원료 원산지가 영국산으로 신뢰가 가며 성분이 좋아 컨디션 유지에 도움이 됨</t>
+          <t>영국산 검증 원료 — 품질이 보증된 영국산 고려은단 비타민C 원료를 사용하여 깊은 신뢰감을 줌</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>확실한 컨디션 체감 — 꾸준히 복용할 때 피부 상태 개선이나 피로 완화 측면에서 긍정적인 체감이 큼</t>
+          <t>꾸준한 건강 개선 — 장기적으로 복용 시 피부톤 조절이나 몸의 면역력 관리에 직접적인 도움을 줌</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>매우 시고 부담스러운 맛 — 분말 제형 특유의 극심한 신맛과 불호가 갈리는 쓴맛으로 인해 목넘김이 힘듦</t>
+          <t>섭취 곤란한 신맛 — 가루 제형 특성상 신맛의 세기가 지나치게 무척 강해 먹기에 거북함</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>가루 제형의 불편함 — 가루 형태로 되어 있어 복용 시 불편하며 알약이나 캡슐 제형으로 대체되기를 희망함</t>
+          <t>불편한 제형 타입 — 분말 비타민 타입이라 섭취가 원활하지 않아 삼키기 좋은 캡슐 형태를 원함</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -2678,22 +3182,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>훌륭한 맛과 풍미 — 말차, 유자 등 상큼하고 기호성이 좋은 맛으로 구성되어 거부감 없이 맛있게 먹기 좋음</t>
+          <t>맛과 소화력 조화 — 유자맛 등으로 효소 특유의 냄새 없이 맛이 훌륭하며 식후 소화가 더 잘됨</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>매력적인 굿즈 구성 — 포토카드와 엽서 등 리센느 에디션 전용 굿즈의 품질이 우수하여 소장 가치가 높음</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>원활한 소화 작용 — 식사 후에 먹었을 때 속이 금방 편안해지고 더부룩한 소화 불량 증상이 개선됨</t>
-        </is>
-      </c>
+          <t>매력적인 굿즈 증정 — 한정판 리센느의 미공개 포토카드와 엽서가 동봉되어 수집적 가치가 높음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>사은품 누락 발생 — 포장 상태를 꼼꼼히 확인했음에도 일부 포토카드 굿즈 구성품이 누락되어 배송됨</t>
+          <t>증정 사은품 누락 — 패키지 개봉 시 핵심 구성인 아이돌 포토카드가 담겨 있지 않고 누락되어 옴</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -2710,55 +3210,51 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260923111828_e9badd52c1a54899b5226c1eae768639.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>60</v>
+        <v>1689</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 식감 — 닭가슴살임에도 퍽퍽함 없이 부드럽고 촉촉하며 비린 잡내가 나지 않아 맛있음</t>
+          <t>체감되는 속의 편안 — 밀가루 등 식사 후 더부룩한 체증이 생길 때 섭취하면 빠르게 속이 가벼워짐</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>다채로운 식단 구성 — 소스 닭가슴살, 스테이크, 주먹밥 등 구성이 매우 다양하여 다이어트 중 질리지 않음</t>
+          <t>대중적인 곡물 맛 — 효소 제품 특유의 비린 맛 없이 고소하고 달달한 고구마 향이 풍겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>합리적인 가성비 — 행사나 세일 구매 시 높은 가성비를 제공하여 대량으로 냉장고에 쟁여두기 유용함</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>특정 제품 구성의 부재 — 가장 인기가 높은 파우치형 그릴 형태의 단독 제품이 구성에 빠져 있어 다소 아쉬움</t>
-        </is>
-      </c>
+          <t>풍부한 패키지 증정 — 저렴한 세일가 대비 사은품 단백질바와 곡물 차 등이 알차게 동봉됨</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -2773,51 +3269,51 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>64,200원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260923111828_e9badd52c1a54899b5226c1eae768639.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>1689</v>
+        <v>61</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>편안한 소화와 위장 — 밀가루 음식을 섭취한 뒤 속이 더부룩할 때 먹으면 금방 편안해지고 소화가 잘됨</t>
+          <t>촉촉하고 부드러운 맛 — 닭가슴살 본래의 퍽퍽함이 전혀 느껴지지 않을 정도로 식감이 부드럽고 마싯음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>구수하고 대중적인 맛 — 호불호 없는 구수한 고구마 맛이 나서 누구나 거부감 없이 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>푸짐한 사은품 구성 — 효소 제품과 더불어 함께 증정된 단백질바와 곡물차 등 사은품 퀄리티가 만족스러움</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>다채롭고 질리지 않음 — 소스 닭가슴살, 스테이크, 볼 등 여러 종류가 고루 담겨 장기간 식단 관리에 유용함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>선호 옵션 부재 — 패키지 안에서 가장 평이 좋은 파우치형 그릴 형태의 닭가슴살 옵션이 빠져 있음</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -2863,22 +3359,18 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>감동을 주는 패키지 — 오간자 포장과 함께 동봉된 플리츠백 패키지가 고급스럽고 예뻐 감동적인 선물이 됨</t>
+          <t>고품격 기프트 디자인 — 오간자 패키지와 예쁜 플리츠백이 훌륭하게 장식되어 선물 수령 시 큰 기쁨을 줌</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>거부감 없는 상큼한 맛 — 특유의 비릿한 콜라겐 냄새 없이 맛이 훌륭하여 매일 기분 좋게 섭취하기 편함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>피로 해소와 활력 증진 — 피부 탄력 개선에 대한 기대감과 더불어 복용 후 몸의 피곤함이 한결 덜해짐</t>
-        </is>
-      </c>
+          <t>높은 기호성과 복용성 — 새콤한 맛의 비오틴 앰플 타입으로 물 없이 원스톱으로 맛있게 복용 가능함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>부담스러운 가격 장벽 — 제품 퀄리티와 명성은 우수하나 가격대가 높아 상시 구매를 결정하기에는 부담이 됨</t>
+          <t>지속 구매의 가격 부담 — 성분이나 효능은 매우 좋으나 일일 단위 단가가 높아 세일 때만 재구매하게 됨</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -2926,23 +3418,23 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>뛰어난 풍미와 포만감 — 소스 맛이 아주 훌륭하고 닭가슴살 한 개만 잘 씹어 먹어도 포만감이 오래 지속됨</t>
+          <t>확실한 포만감 — 하나만 먹어도 포만감이 든든히 채워지며 자극적인 소스 맛으로 훌륭한 식사 대안임</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>실용적인 사은품 보냉백 — 증정되는 보냉 가방의 디자인이 세련되고 크기도 적당하여 실용적으로 들고 다니기 좋음</t>
+          <t>도시락 보냉백 증정 — 사은품으로 따라오는 보냉백 디자인과 마감이 훌륭하여 단독 가방으로도 손색없음</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>오배송 및 미흡한 대처 — 동일한 맛이 중복으로 오거나 팩 개수가 잘못 배송되는 등 오류가 있으나 판매자 답변이 없음</t>
+          <t>부실한 진공 실링 — 일부 팩의 내부 포장 불량으로 내용물이 찢어지거나 소스가 줄줄 새어 주변에 묻음</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>비닐 포장 및 터짐 불량 — 진공 비닐 포장이 밀착되지 않고 헐렁하게 포장되어 배송 중 소스가 터져 흐르는 하자가 있음</t>
+          <t>불합리한 오배송 발생 — 주문서와 다르게 팩의 구성이 다르게 뒤바뀌거나 특정 팩이 누락되어 배송됨</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -2950,7 +3442,7 @@
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2958,51 +3450,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>20,000원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>217</v>
+        <v>904</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 고유의 비리고 텁텁한 맛이 전혀 없고 초코나 모카라떼처럼 맛있음</t>
+          <t>원활한 소화 작용 — 만성적 소화 장해와 변비가 있을 때 꾸준히 복용 시 배변에 유익한 피드백을 제공함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>확실한 포만감 형성 — 운동 후나 가벼운 간식이 당길 때 섭취하면 배고픔을 잡아주어 포만감 관리에 유용함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>피부에 이로운 성분 — 분리유청단백질(WPI)을 함유하여 소화 흡수가 잘되고 피부 트러블 걱정을 덜어줌</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>혜택 넓은 구성품 — 가성비 좋은 단독 판매가에 저당 과자 등 추가 간식 증정이 포함되어 넉넉함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>미세한 풍미의 변동 — 이전에 동일하게 구매했던 제품과 대비했을 때 고소한 감칠맛 등 미묘하게 맛이 달라짐</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3048,18 +3540,18 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 퍽퍽함 없이 촉촉하고 부드러우며 간이 적당하여 다이어트 식사로 아주 제격임</t>
+          <t>비리지 않고 쫄깃함 — 수분기가 촉촉하며 닭 특유의 냄새나 누린내 없이 간이 정갈하게 배어 맛이 좋음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>간편하고 손쉬운 조리 — 전자레인지로 쉽게 데워 먹을 수 있으며 볼 형태는 샐러드 등에 곁들여 먹기 편함</t>
+          <t>간편하고 빠른 식사 — 한입 크기로 개별 포장된 볼 타입이 포함되어 전자레인지에 짧게 데우면 식단이 완성됨</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>다소 지연되는 배송 — 제품의 품질과 가성비는 아주 우수하나 배송 처리 속도가 다소 느린 면이 있음</t>
+          <t>다소 불만족스러운 배송 — 신선도가 요구되는 닭가슴살 제품임에도 배송 완료까지의 소요 기간이 다소 느림</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -3076,48 +3568,48 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20,000원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/10908258</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260910161144_21b98063441d4fba961ab0b7baf37feb.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>903</v>
+        <v>1174</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>소화 및 변비 개선 — 꾸준히 복용한 결과 속이 가벼워지고 더부룩함 완화 및 배변 활동에 도움을 봄</t>
+          <t>부담 없는 가공 맛 — 알로에나 요구르트 본래의 맛을 인위적인 화학 가공 향 없이 건강하게 표현해 냄</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>합리적인 가성비와 혜택 — 다소 고가의 효소를 파격적인 구성과 추가 증정, 저당 칩 사은품 혜택으로 저렴히 삼</t>
+          <t>향상되는 운동 능력 — 운동 중 충분히 전해질과 활력을 채워 주어 지치지 않고 고강도 집중력이 가능함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>정성스러운 제품 포장 — 깔끔하고 꼼꼼하게 포장되어 있어 제품을 받아 개봉할 때 기분이 좋아짐</t>
+          <t>풍족한 대용량 가치 — 대용량 통 형태로 구성되어 가성비 높은 경제적인 장기 복용을 가능케 함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3135,58 +3627,62 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10908258</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260910161144_21b98063441d4fba961ab0b7baf37feb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1173</v>
+        <v>21</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>역대급의 뛰어난 맛 — 아미노산 특유의 인위적인 이취 없이 진짜 요구르트나 매실 음료 같은 훌륭한 맛이 남</t>
+          <t>유의미한 숙취 예방 — 음주 전에 챙겨 마시면 다음 날 자고 일어났을 때 머리 무거움이나 피로감이 확실히 덜함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>우수한 운동 부스팅 — 운동 중 수분 및 전해질을 신속히 보충해 주어 운동 시 지구력과 수행능력이 향상됨</t>
+          <t>고품격 패키지 장식 — 선물용으로 기품이 넘치게 단장된 보라색 쇼핑백과 정품 스티커 마감이 마음에 듦</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>넉넉하고 든든한 용량 — 오랜 기간 섭취할 수 있을 만큼 용량이 푸짐하여 가격 대비 성능이 뛰어남</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>안심할 수 있는 무첨가 — 인위적인 합성착색료나 화학 향료를 배제하고 자연 약재를 고함량 추출하여 보장됨</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>개인 편차 있는 쓴맛 — 조금 걸쭉한 농축액 형태이며 쌍화탕이나 한약 고유의 쓴 기미가 있어 불호가 갈림</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3194,51 +3690,51 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>21</v>
+        <v>1535</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>탁월한 숙취 예방 효과 — 음주 전후 섭취 시 확실히 다음 날 아침의 두통, 울렁거림 및 특유의 피로가 현저히 감소함</t>
+          <t>효과 높은 활력 보충 — 아침 기상 시 한결 상쾌하게 일어날 수 있게 해주고 아르기닌 에너지로 피로 완화에 도움을 줌</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>고급 선물 패키지 — 고급스러운 보라색 박스 포장과 리본 손잡이 쇼핑백이 세트로 구성되어 정성 담긴 선물로 좋음</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>위생적인 개별 포장 — 1회 섭취 분량씩 스틱 제형으로 소포장되어 외출 및 술자리에 부담 없이 휴대하기 유용함</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>완벽한 영양소 조율 — 매일 쌓인 피로를 해소하는 아르기닌 마카와 간 활성의 밀크씨슬 복합 구성이 유용함</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>종이 쇼핑백 불량 — 전달용으로 세트 동봉되는 종이가방의 양 끝 고정 끈 부분이 누락되어 전달 시 곤란함</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -3388,12 +3884,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -3445,12 +3941,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>정관장</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>정관장</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -3502,12 +3998,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -3560,7 +4056,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16227</v>
+        <v>16228</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15540</v>
@@ -3575,16 +4071,16 @@
         <v>813</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8741</v>
+        <v>8742</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>811</v>
       </c>
       <c r="J7" s="3" t="n">
+        <v>1743</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>780</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>1742</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>950</v>
@@ -3598,67 +4094,65 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복과 활력 — 지치고 피로할 때 섭취 시 에너지가 충전되고 활력이 솟아나는 효과가 있음
-선물용으로 제격 — 패키지가 고급스러우며 받는 사람과 주는 사람 모두의 만족도가 매우 높음
-우수한 맛과 제형 — 액상과 알약 형태로 구성되어 맛이 좋고 부담 없이 든든하게 복용 가능함</t>
+          <t>탁월한 피로 회복 — 지치고 피로할 때 먹으면 힘이 나고 활력이 돋음
+편리한 섭취 방식 — 액상과 알약 형태로 섭취가 쉬우며 맛이 좋아 에너지를 충전하기 좋음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선과 활력 — 학업이나 업무로 지치고 피곤할 때 먹으면 에너지가 충전되는 느낌을 받음
-편리한 휴대성 — 한 손에 들어오는 콤팩트한 크기에 액상과 알약이 함께 있어 외출 시 챙기기 편함
-높은 선물 만족도 — 포장이 깔끔하고 배송이 빨라 지인들에게 센스 있는 선물로 추천할 만함</t>
+          <t>확실한 활력 충전 — 과중한 업무나 학업으로 지쳤을 때 복용하면 빠른 피로 완화에 도움을 줌
+우수한 휴대 편의 — 알약과 액상이 콤팩트한 한 포에 같이 있어 외출이나 여행 시 챙기기 편함
+센스 있는 패키지 — 포장이 무척 깔끔하고 고급스러워 주변 지인들에게 선물용으로 기분 좋게 전달 가능함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 완화 — 복용한 다음 날 피로감이 덜하고 힘들 때 신속하게 에너지를 채워줌
-기분 좋은 선물 — 직접 구매하기엔 다소 부담스러운 가격의 인기 제품을 선물로 받아 만족도가 높음</t>
+          <t>기력 보충에 효과 — 환절기에 기운을 차릴 수 있게 돕고 힘들 때 일시적인 피로 회복 효과가 있음
+높은 선물 선호도 — 다소 고가의 영양제라 직접 구매하기보다 선물로 받았을 때 만족도가 무척 높음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 식감 — 쫄깃하고 달콤한 젤리 제형으로 영양제 느낌 없이 간식처럼 맛있게 먹을 수 있음
-간편한 섭취 방식 — 알약을 잘 삼키지 못하거나 수술 후 목넘김이 힘든 사람도 편하게 씹어서 섭취함
-귀여운 패키지 디자인 — 감귤 모양의 케이스 디자인과 동봉된 키캡 등의 구성품이 무척 귀여움</t>
+          <t>맛있는 젤리 제형 — 새콤달콤하고 맛과 향이 훌륭하여 간식처럼 부담 없이 챙겨 먹기 좋음
+편리한 목넘김 — 알약을 잘 넘기지 못하거나 수술 후 삼키기 어려운 분들도 쉽게 씹어서 섭취 가능함
+아기자기한 부자재 — 손잡이가 달린 귀여운 감귤 패키지와 소장 가치 있는 키캡 사은품이 동봉됨</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>우수한 휴대와 복용 — 바쁜 출근길에 가볍게 하나씩 챙겨 나갈 수 있고 마시는 형태라 복용이 편리함
-효과적인 피로 개선 — 피로 완화와 활력 충전에 뛰어나며 환절기 건강 관리용으로 추천함</t>
+          <t>우수한 휴대성 — 출근길에 가볍게 챙겨 나갈 수 있는 개별 스틱 패키지로 휴대와 보관이 편함
+간편한 섭취 방식 — 마시는 올인원 형태로 설계되어 삼키기 부드럽고 덜 피곤한 효과를 체감함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 — 자기 전에 먹으면 아침에 기상할 때 몸이 무겁지 않고 피로 해소에 확실히 도움됨
-알찬 패키지 구성 — 선물하기 단독 에디션으로 추가 증정분이 포함되어 알차고 깔끔한 첫인상을 줌</t>
+          <t>개선되는 아침 피로 — 취침 전 복용 시 다음 날 아침 일어날 때 몸 상태가 가볍게 느껴짐
+실속 있는 패키지 — 7입 본품에 2입을 추가 증정하는 알찬 패키지 구성으로 선물 전달용에 적합함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 고급스러운 박스와 종이가방이 동봉되어 격식 있는 명절 선물용으로 매우 훌륭함
-면역력 및 활력 충전 — 피로를 빠르게 해결해주고 환절기 감기 예방 및 면역력을 키우는 데 탁월함</t>
+          <t>고품격 패키징 — 포장 외형이 매우 단정하고 예쁘며 종이가방이 기본 제공되어 품격 있는 선물로 좋음
+즉각적인 체력 개선 — 피로에 지쳤을 때 복용 즉시 에너지가 생겨 기운을 차릴 수 있게 도움을 줌</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤형 선택 옵션 — 남성과 여성을 위한 포뮬러가 따로 설계 및 구분되어 있어 성별에 맞춰 선물하기 좋음
-거부감 없는 맛과 제형 — 비타민 특유의 거북하고 쓴맛이 없어 복용하기에 부담감이 없고 섭취가 편리함
-풍부한 영양 성분 — 기존 이뮨 라인보다 함유된 영양소가 더 많아 피로 회복에 탁월한 효과가 있음</t>
+          <t>혁신적인 특수 마개 — 빛과 습기에 예민한 분말과 액상을 분리 밀폐하는 4중 구조 프레스 캡을 사용하여 안전함
+매우 빠른 총알 배송 — 선물 배송지 입력 후 만 하루 만에 받아볼 수 있을 만큼 무척 신속함
+부담 없는 가격대 — 고급스러운 외관 대비 가격 부담이 적어 출산 선물이나 연령대 있는 생일 선물용에 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>혁신적인 밀폐 용기 — 프레스버튼캡 구조로 빛과 습기에 약한 분말 원료를 상하지 않게 완벽히 보관함
-만족스러운 맛과 영양 — 맛과 영양을 모두 잡았으며 음주나 육아 등으로 지친 몸의 피로감을 확실히 덜어줌
-품격 있는 가성비 선물 — 패키지가 은근히 묵직하고 고급스러워 받는 사람에게 기분 좋은 가성비 선물이 됨</t>
+          <t>성별 맞춤 선택 — 남성과 여성을 위한 최적화 영양이 다르게 설계되어 맞춤형 관리가 가능함
+우수한 목넘김 — 영양제 고유의 불쾌한 쓴맛이나 냄새가 적어 진득하고 건강하게 섭취하기 좋음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>신뢰도 높은 원산지 — 원료 원산지가 영국산으로 신뢰가 가며 성분이 좋아 컨디션 유지에 도움이 됨
-확실한 컨디션 체감 — 꾸준히 복용할 때 피부 상태 개선이나 피로 완화 측면에서 긍정적인 체감이 큼</t>
+          <t>영국산 검증 원료 — 품질이 보증된 영국산 고려은단 비타민C 원료를 사용하여 깊은 신뢰감을 줌
+꾸준한 건강 개선 — 장기적으로 복용 시 피부톤 조절이나 몸의 면역력 관리에 직접적인 도움을 줌</t>
         </is>
       </c>
     </row>
@@ -3672,18 +4166,18 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>선물 발송자 미표기 — 보낸 사람이 누구인지 기재되어 있지 않고 관련 문의 시 고객센터의 답변이 모호함</t>
+          <t>보낸이 확인 불가 — 선물 보낸 사람이 누구인지 표시되지 않고 관련 문의에 불분명하게 답변함</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>배송 포장의 아쉬움 — 전용 쇼핑백이 누락되고 별도의 보완 포장 없이 택배 상자에 본품만 배송되어 당황스러움</t>
+          <t>아쉬운 배송 포장 — 타 쇼핑몰과 달리 쇼핑백이나 고정용 완충 없이 일반 박스에 그냥 배송되어 아쉬움</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>다소 빈약한 부피감 — 소포장 제품 특성상 직접 보았을 때 선물로서 풍성해 보이는 느낌은 덜함</t>
+          <t>부족해 보이는 볼륨 — 소포장 위주로 디자인되어 제품 수령 시 겉으로 풍성해 보이지 않을 수 있음</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
@@ -3691,8 +4185,8 @@
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>매우 시고 부담스러운 맛 — 분말 제형 특유의 극심한 신맛과 불호가 갈리는 쓴맛으로 인해 목넘김이 힘듦
-가루 제형의 불편함 — 가루 형태로 되어 있어 복용 시 불편하며 알약이나 캡슐 제형으로 대체되기를 희망함</t>
+          <t>섭취 곤란한 신맛 — 가루 제형 특성상 신맛의 세기가 지나치게 무척 강해 먹기에 거북함
+불편한 제형 타입 — 분말 비타민 타입이라 섭취가 원활하지 않아 삼키기 좋은 캡슐 형태를 원함</t>
         </is>
       </c>
     </row>
@@ -3739,12 +4233,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>39,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>59,800원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>39,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -3917,27 +4411,27 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -3954,47 +4448,47 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -4011,14 +4505,14 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
-        </is>
-      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
           <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
@@ -4031,7 +4525,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -4041,17 +4535,17 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
     </row>
@@ -4102,10 +4596,10 @@
         <v>185</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>60</v>
+        <v>1689</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1689</v>
+        <v>61</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>754</v>
@@ -4114,19 +4608,19 @@
         <v>152</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>217</v>
+        <v>904</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>69</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>903</v>
+        <v>1174</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1173</v>
+        <v>21</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>21</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4137,70 +4631,65 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>훌륭한 맛과 풍미 — 말차, 유자 등 상큼하고 기호성이 좋은 맛으로 구성되어 거부감 없이 맛있게 먹기 좋음
-매력적인 굿즈 구성 — 포토카드와 엽서 등 리센느 에디션 전용 굿즈의 품질이 우수하여 소장 가치가 높음
-원활한 소화 작용 — 식사 후에 먹었을 때 속이 금방 편안해지고 더부룩한 소화 불량 증상이 개선됨</t>
+          <t>맛과 소화력 조화 — 유자맛 등으로 효소 특유의 냄새 없이 맛이 훌륭하며 식후 소화가 더 잘됨
+매력적인 굿즈 증정 — 한정판 리센느의 미공개 포토카드와 엽서가 동봉되어 수집적 가치가 높음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 식감 — 닭가슴살임에도 퍽퍽함 없이 부드럽고 촉촉하며 비린 잡내가 나지 않아 맛있음
-다채로운 식단 구성 — 소스 닭가슴살, 스테이크, 주먹밥 등 구성이 매우 다양하여 다이어트 중 질리지 않음
-합리적인 가성비 — 행사나 세일 구매 시 높은 가성비를 제공하여 대량으로 냉장고에 쟁여두기 유용함</t>
+          <t>체감되는 속의 편안 — 밀가루 등 식사 후 더부룩한 체증이 생길 때 섭취하면 빠르게 속이 가벼워짐
+대중적인 곡물 맛 — 효소 제품 특유의 비린 맛 없이 고소하고 달달한 고구마 향이 풍겨 먹기 좋음
+풍부한 패키지 증정 — 저렴한 세일가 대비 사은품 단백질바와 곡물 차 등이 알차게 동봉됨</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>편안한 소화와 위장 — 밀가루 음식을 섭취한 뒤 속이 더부룩할 때 먹으면 금방 편안해지고 소화가 잘됨
-구수하고 대중적인 맛 — 호불호 없는 구수한 고구마 맛이 나서 누구나 거부감 없이 맛있게 먹을 수 있음
-푸짐한 사은품 구성 — 효소 제품과 더불어 함께 증정된 단백질바와 곡물차 등 사은품 퀄리티가 만족스러움</t>
+          <t>촉촉하고 부드러운 맛 — 닭가슴살 본래의 퍽퍽함이 전혀 느껴지지 않을 정도로 식감이 부드럽고 마싯음
+다채롭고 질리지 않음 — 소스 닭가슴살, 스테이크, 볼 등 여러 종류가 고루 담겨 장기간 식단 관리에 유용함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>감동을 주는 패키지 — 오간자 포장과 함께 동봉된 플리츠백 패키지가 고급스럽고 예뻐 감동적인 선물이 됨
-거부감 없는 상큼한 맛 — 특유의 비릿한 콜라겐 냄새 없이 맛이 훌륭하여 매일 기분 좋게 섭취하기 편함
-피로 해소와 활력 증진 — 피부 탄력 개선에 대한 기대감과 더불어 복용 후 몸의 피곤함이 한결 덜해짐</t>
+          <t>고품격 기프트 디자인 — 오간자 패키지와 예쁜 플리츠백이 훌륭하게 장식되어 선물 수령 시 큰 기쁨을 줌
+높은 기호성과 복용성 — 새콤한 맛의 비오틴 앰플 타입으로 물 없이 원스톱으로 맛있게 복용 가능함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 풍미와 포만감 — 소스 맛이 아주 훌륭하고 닭가슴살 한 개만 잘 씹어 먹어도 포만감이 오래 지속됨
-실용적인 사은품 보냉백 — 증정되는 보냉 가방의 디자인이 세련되고 크기도 적당하여 실용적으로 들고 다니기 좋음</t>
+          <t>확실한 포만감 — 하나만 먹어도 포만감이 든든히 채워지며 자극적인 소스 맛으로 훌륭한 식사 대안임
+도시락 보냉백 증정 — 사은품으로 따라오는 보냉백 디자인과 마감이 훌륭하여 단독 가방으로도 손색없음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 고유의 비리고 텁텁한 맛이 전혀 없고 초코나 모카라떼처럼 맛있음
-확실한 포만감 형성 — 운동 후나 가벼운 간식이 당길 때 섭취하면 배고픔을 잡아주어 포만감 관리에 유용함
-피부에 이로운 성분 — 분리유청단백질(WPI)을 함유하여 소화 흡수가 잘되고 피부 트러블 걱정을 덜어줌</t>
+          <t>원활한 소화 작용 — 만성적 소화 장해와 변비가 있을 때 꾸준히 복용 시 배변에 유익한 피드백을 제공함
+혜택 넓은 구성품 — 가성비 좋은 단독 판매가에 저당 과자 등 추가 간식 증정이 포함되어 넉넉함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 퍽퍽함 없이 촉촉하고 부드러우며 간이 적당하여 다이어트 식사로 아주 제격임
-간편하고 손쉬운 조리 — 전자레인지로 쉽게 데워 먹을 수 있으며 볼 형태는 샐러드 등에 곁들여 먹기 편함</t>
+          <t>비리지 않고 쫄깃함 — 수분기가 촉촉하며 닭 특유의 냄새나 누린내 없이 간이 정갈하게 배어 맛이 좋음
+간편하고 빠른 식사 — 한입 크기로 개별 포장된 볼 타입이 포함되어 전자레인지에 짧게 데우면 식단이 완성됨</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>소화 및 변비 개선 — 꾸준히 복용한 결과 속이 가벼워지고 더부룩함 완화 및 배변 활동에 도움을 봄
-합리적인 가성비와 혜택 — 다소 고가의 효소를 파격적인 구성과 추가 증정, 저당 칩 사은품 혜택으로 저렴히 삼
-정성스러운 제품 포장 — 깔끔하고 꼼꼼하게 포장되어 있어 제품을 받아 개봉할 때 기분이 좋아짐</t>
+          <t>부담 없는 가공 맛 — 알로에나 요구르트 본래의 맛을 인위적인 화학 가공 향 없이 건강하게 표현해 냄
+향상되는 운동 능력 — 운동 중 충분히 전해질과 활력을 채워 주어 지치지 않고 고강도 집중력이 가능함
+풍족한 대용량 가치 — 대용량 통 형태로 구성되어 가성비 높은 경제적인 장기 복용을 가능케 함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>역대급의 뛰어난 맛 — 아미노산 특유의 인위적인 이취 없이 진짜 요구르트나 매실 음료 같은 훌륭한 맛이 남
-우수한 운동 부스팅 — 운동 중 수분 및 전해질을 신속히 보충해 주어 운동 시 지구력과 수행능력이 향상됨
-넉넉하고 든든한 용량 — 오랜 기간 섭취할 수 있을 만큼 용량이 푸짐하여 가격 대비 성능이 뛰어남</t>
+          <t>유의미한 숙취 예방 — 음주 전에 챙겨 마시면 다음 날 자고 일어났을 때 머리 무거움이나 피로감이 확실히 덜함
+고품격 패키지 장식 — 선물용으로 기품이 넘치게 단장된 보라색 쇼핑백과 정품 스티커 마감이 마음에 듦
+안심할 수 있는 무첨가 — 인위적인 합성착색료나 화학 향료를 배제하고 자연 약재를 고함량 추출하여 보장됨</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>탁월한 숙취 예방 효과 — 음주 전후 섭취 시 확실히 다음 날 아침의 두통, 울렁거림 및 특유의 피로가 현저히 감소함
-고급 선물 패키지 — 고급스러운 보라색 박스 포장과 리본 손잡이 쇼핑백이 세트로 구성되어 정성 담긴 선물로 좋음
-위생적인 개별 포장 — 1회 섭취 분량씩 스틱 제형으로 소포장되어 외출 및 술자리에 부담 없이 휴대하기 유용함</t>
+          <t>효과 높은 활력 보충 — 아침 기상 시 한결 상쾌하게 일어날 수 있게 해주고 아르기닌 에너지로 피로 완화에 도움을 줌
+완벽한 영양소 조율 — 매일 쌓인 피로를 해소하는 아르기닌 마카와 간 활성의 밀크씨슬 복합 구성이 유용함</t>
         </is>
       </c>
     </row>
@@ -4212,35 +4701,47 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>사은품 누락 발생 — 포장 상태를 꼼꼼히 확인했음에도 일부 포토카드 굿즈 구성품이 누락되어 배송됨</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>특정 제품 구성의 부재 — 가장 인기가 높은 파우치형 그릴 형태의 단독 제품이 구성에 빠져 있어 다소 아쉬움</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
+          <t>증정 사은품 누락 — 패키지 개봉 시 핵심 구성인 아이돌 포토카드가 담겨 있지 않고 누락되어 옴</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>선호 옵션 부재 — 패키지 안에서 가장 평이 좋은 파우치형 그릴 형태의 닭가슴살 옵션이 빠져 있음</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 가격 장벽 — 제품 퀄리티와 명성은 우수하나 가격대가 높아 상시 구매를 결정하기에는 부담이 됨</t>
+          <t>지속 구매의 가격 부담 — 성분이나 효능은 매우 좋으나 일일 단위 단가가 높아 세일 때만 재구매하게 됨</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>오배송 및 미흡한 대처 — 동일한 맛이 중복으로 오거나 팩 개수가 잘못 배송되는 등 오류가 있으나 판매자 답변이 없음
-비닐 포장 및 터짐 불량 — 진공 비닐 포장이 밀착되지 않고 헐렁하게 포장되어 배송 중 소스가 터져 흐르는 하자가 있음</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>부실한 진공 실링 — 일부 팩의 내부 포장 불량으로 내용물이 찢어지거나 소스가 줄줄 새어 주변에 묻음
+불합리한 오배송 발생 — 주문서와 다르게 팩의 구성이 다르게 뒤바뀌거나 특정 팩이 누락되어 배송됨</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>미세한 풍미의 변동 — 이전에 동일하게 구매했던 제품과 대비했을 때 고소한 감칠맛 등 미묘하게 맛이 달라짐</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>다소 지연되는 배송 — 제품의 품질과 가성비는 아주 우수하나 배송 처리 속도가 다소 느린 면이 있음</t>
+          <t>다소 불만족스러운 배송 — 신선도가 요구되는 닭가슴살 제품임에도 배송 완료까지의 소요 기간이 다소 느림</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>개인 편차 있는 쓴맛 — 조금 걸쭉한 농축액 형태이며 쌍화탕이나 한약 고유의 쓴 기미가 있어 불호가 갈림</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>종이 쇼핑백 불량 — 전달용으로 세트 동봉되는 종이가방의 양 끝 고정 끈 부분이 누락되어 전달 시 곤란함</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4255,14 +4756,14 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>46,900원</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>64,200원</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>46,900원</t>
-        </is>
-      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t>65,900원</t>
@@ -4275,7 +4776,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>20,000원</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -4285,17 +4786,17 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>20,000원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>27,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4986,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4493,7 +4994,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 10정 10일분</t>
+          <t>대웅제약 MSM 90정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4503,39 +5004,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000149&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/gVoECGdnaBQU8HtRPGFz600000149_00_00gVoECGdnaBQU8HtRPGFz.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>778</v>
+        <v>1025</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>식후 식곤증 예방 — 식사 후에 복용하면 급격한 혈당 상승을 조절해 주어 낮 시간 졸음 완화에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>극강의 압도적 가성비 — 다이소 특유의 매우 저렴하고 착한 가격으로 우수한 혈당 관리 영양제를 구비할 수 있음</t>
-        </is>
-      </c>
+          <t>저렴하고 착한 공급가 — 다이소 특유의 압도적인 가성비와 부담 없는 가격으로 뼈 마디 건강 관리에 제격임</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>아쉬운 정제 맛 — 입에 닿았을 때 느껴지는 특유의 맛이 별로여서 삼키기 부담스러운 단점이 있음</t>
+          <t>많은 정제 복용 횟수 — 일일 섭취 기준 충족을 위해 한 번에 3알씩 챙겨야 하므로 삼킬 때 누락되기 쉬움</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -4544,7 +5041,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4552,49 +5049,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>129</v>
+        <v>779</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>효과적인 붓기 개선 — 아침에 얼굴이 자주 붓거나 붓기 관리가 필요할 때 간편히 복용하면 개선 효과가 있음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>달콤하고 맛있는 캔디 — 특유의 약 냄새 없이 일반 맛있는 사탕처럼 즐겁게 먹을 수 있어 편의성이 높음</t>
-        </is>
-      </c>
+          <t>식후 식곤증 관리 — 식사 후 졸음이 쏟아지는 현상을 미연에 관리하는 데 효과적인 도움을 받음</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>빈번한 일시 품절 현상 — 매장이나 온라인 몰에서 자주 품절되어 재고가 부족해 제때 구매하기가 쉽지 않음</t>
+          <t>알약의 아쉬운 미각 — 정제를 삼키기 전 표면에서 다소 씁쓸하거나 나쁜 맛이 느껴져 삼키는 과정이 힘듦</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -4603,7 +5096,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4611,12 +5104,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>동국제약 마데카 리포좀 레티놀C 20포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4626,28 +5119,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910601&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250502/YBmj8aPscGIkmB6O6RuJ610910601_00_00YBmj8aPscGIkmB6O6RuJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>654</v>
+        <v>7069</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>편리한 섭취 방식 — 물 없이도 가볍게 입안에 털어 넣어 녹여 먹을 수 있는 가루 타입이라 먹기 편함</t>
+          <t>삼키기 좋은 크기 — 코엔자임 정제의 캡슐 사이즈가 아담하고 매우 작아 목에 부드럽게 넘어감</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>우수한 맛과 가성비 — 상큼하고 좋은 맛을 지녔으며 동국제약 제품답게 저렴하지만 성분이 우수함</t>
+          <t>뛰어난 위장 유연성 — 복용 후 하복부에서 신물이나 미슥거리는 자극 없이 속 편하게 일상 유지가 됨</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -4658,7 +5151,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4666,54 +5159,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2536</v>
+        <v>3610</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>상큼한 파인애플 맛 — 상큼달콤한 파인애플 사탕 맛으로 남녀노소 누구나 기분 좋게 챙겨 먹기 적합함</t>
+          <t>체감되는 숙면 유도 — 복용 후 새벽에 뒤척이거나 갑자기 깨는 일 없이 안정감 있는 깊은 수면이 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>하체 붓기 완화 효과 — 다리 부종 완화에 효과가 있어 저녁마다 다리가 무겁거나 쉽게 붓는 이들에게 유용함</t>
+          <t>부담 없는 장기 보충 — 일조량이 부족할 때 비타민D를 저렴하게 대량 구비하여 온 가족이 먹기에 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>아쉬운 개별 함량 — 1알로는 최적 함량을 채우기 다소 어려워 총 2정씩 꼬박꼬박 챙겨 먹어야 함</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4721,12 +5218,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4736,32 +5233,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>282</v>
+        <v>6593</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>복용이 손쉬운 필름 — 입천장이나 혀에 간편하게 부착하여 녹여 먹는 구강용 필름 제형이라 섭취가 매우 쉬움</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>간결한 일회 복용 — 번거롭게 수시로 먹을 필요 없이 하루 한 정만 간편하게 섭취해 관리가 쉬움</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>한 달 단위 안심 보관 — 딱 한 달 동안 먹기 좋게 분량 조절이 되어 위생적으로 휴대하고 유지하기 편리함</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>개인에 따라 다른 맛 — 맛의 기호성에 차이가 있어 일부 이용자에게는 매우 맛이 없고 먹기 곤욕스럽게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -4776,54 +5273,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1597</v>
+        <v>833</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>이중 배합의 건강 케어 — 장 건강을 위한 유산균 공급은 물론 식후 혈당 케어까지 캡슐 하나로 동시에 관리함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>부담 없는 저렴한 단가 — 매일 섭취해도 가격에 대한 지출 부담이 전혀 없으며 캡슐 타입이라 휴대에도 용이함</t>
-        </is>
-      </c>
+          <t>우수한 경비 조절 — 몸보신 아르기닌 입문용으로 고가의 세트 대비 부담 없는 비용으로 가볍게 활력을 즐김</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>미약한 체력 각성 — 체감되는 즉각적인 에너지 대사나 신체 충전 효과를 기대하는 데에는 편차가 있음</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4831,7 +5328,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4841,48 +5338,44 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000269&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/LdyaPluhRl2HSeYjB2pX600000269_00_01LdyaPluhRl2HSeYjB2pX.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>547</v>
+        <v>6649</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성 — 여행이나 출장 시 큰 영양제 통을 들고 다닐 필요 없이 필요 소량만 간편히 지참할 수 있음</t>
+          <t>눈가 떨림 장애 해소 — 마그네슘 부족 현상인 눈가 안면 미세 떨림 증세를 신속하게 바로 잡아 줌</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>적은 비린내와 목넘김 — 오메가3 특유의 불쾌한 생선 냄새가 올라오지 않아 목넘김에 거부감이 적음</t>
+          <t>신뢰 가는 성분 처방 — 전문 약사가 가볍게 복용하기 좋게 선별해 준 마그네슘이라 다이소 가격에 안심하고 섭취함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>과도하게 큰 캡슐 크기 — 알약 형태의 오메가3 캡슐 한 알의 크기가 제법 큰 편이어서 물과 삼키기 다소 벅참</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4890,43 +5383,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910967&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000283&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260415/rKimZ2TE65XK1Rwibsnv610910967_00_02rKimZ2TE65XK1Rwibsnv.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/zIbSOpTi3yHSeYULrLdY600000283_00_01zIbSOpTi3yHSeYULrLdY.png</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1543</v>
+        <v>277</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>아이들의 높은 선호도 — 달콤하고 맛있는 샐러드 미니볼 형태로, 약을 기피하는 어린아이들도 아주 좋아함</t>
+          <t>질림 없는 콤팩트 — 큰 용량을 통째로 사서 보관하면 먹다 남기는 분들을 위해 실용적인 미니 소용량임</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>복용의 우수한 편리성 — 한 포씩 소포장 설계되어 보관하기 유용하고 매일 아침 가볍게 뜯어 먹이기 편리함</t>
+          <t>우수한 소량 이동성 — 6일분의 납작하고 아담한 패키지로 출장이나 여행 시 짐 가방 공간을 덜 차지함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -4937,7 +5430,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4945,12 +5438,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4960,34 +5453,30 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1237</v>
+        <v>2888</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>신뢰성 높은 원료 구성 — 저렴한 단가이지만 소연골 유래 원료 기반의 콘드로이친을 채택하여 신뢰할 만함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>깔끔한 한 달 분량 포장 — 30일 단위로 콤팩트하게 개별 상자 포장되어 책상 위에 상시 구비해 두며 먹기 좋음</t>
-        </is>
-      </c>
+          <t>여성 이너 유산균 — 질 건강 이너케어 성분과 장 건강 유산균을 하나의 캡슐에 함축하여 무척 합리적임</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>극심한 배송 지연 발생 — 주문 처리가 매우 늦어 명절 전에 결제한 품목이 오랜 기간 지연 배송되는 현상이 발생함</t>
+          <t>서서히 나타나는 작용 — 복용 즉시 시원하거나 뚜렷한 신체 반응 변화를 명확히 체감하기에는 다소 더딤</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -4996,7 +5485,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5004,12 +5493,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 콜라겐 60정 30일분</t>
+          <t>안국약품 브이팩 여성용 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5019,28 +5508,28 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000138&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235548&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0buLkRj5uSU3KVXDKEhY600000138_00_000buLkRj5uSU3KVXDKEhY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260402/05kyKLN3QpKvymmVHajT968235548_00_0005kyKLN3QpKvymmVHajT.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1361</v>
+        <v>344</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>가성비가 돋보이는 구성 — 가성비가 매우 뛰어나 매일 영양제를 장기적으로 챙겨 먹는 이들에게 유용함</t>
+          <t>여성 전용 밸런스 — 여성 신체 리듬과 성분에 중점을 맞춘 기능 배합을 단 한 포로 해결할 수 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>피부에 와닿는 체감 효과 — 꾸준히 지속적으로 복용할 경우 확실히 전보다 피부 건강과 탄력 회복에 도움을 줌</t>
+          <t>위생적인 간소 섭취 — 외출 시 주머니에 낱개 수납하여 야외에서 가볍게 건강을 채우기 수월함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -5159,27 +5648,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -5189,22 +5678,22 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -5221,47 +5710,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
     </row>
@@ -5273,52 +5762,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 MSM 90정 30일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 마데카 리포좀 레티놀C 20포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콜라겐 60정 30일분</t>
+          <t>안국약품 브이팩 여성용 올인원 멀티 비타민 7포</t>
         </is>
       </c>
     </row>
@@ -5332,16 +5821,16 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
@@ -5366,34 +5855,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>778</v>
+        <v>1025</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>129</v>
+        <v>779</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>654</v>
+        <v>7069</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2536</v>
+        <v>3610</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>282</v>
+        <v>6593</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1597</v>
+        <v>833</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>547</v>
+        <v>6649</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1543</v>
+        <v>277</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1237</v>
+        <v>2888</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1361</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5404,61 +5893,58 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>식후 식곤증 예방 — 식사 후에 복용하면 급격한 혈당 상승을 조절해 주어 낮 시간 졸음 완화에 도움을 줌
-극강의 압도적 가성비 — 다이소 특유의 매우 저렴하고 착한 가격으로 우수한 혈당 관리 영양제를 구비할 수 있음</t>
+          <t>저렴하고 착한 공급가 — 다이소 특유의 압도적인 가성비와 부담 없는 가격으로 뼈 마디 건강 관리에 제격임</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>효과적인 붓기 개선 — 아침에 얼굴이 자주 붓거나 붓기 관리가 필요할 때 간편히 복용하면 개선 효과가 있음
-달콤하고 맛있는 캔디 — 특유의 약 냄새 없이 일반 맛있는 사탕처럼 즐겁게 먹을 수 있어 편의성이 높음</t>
+          <t>식후 식곤증 관리 — 식사 후 졸음이 쏟아지는 현상을 미연에 관리하는 데 효과적인 도움을 받음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>편리한 섭취 방식 — 물 없이도 가볍게 입안에 털어 넣어 녹여 먹을 수 있는 가루 타입이라 먹기 편함
-우수한 맛과 가성비 — 상큼하고 좋은 맛을 지녔으며 동국제약 제품답게 저렴하지만 성분이 우수함</t>
+          <t>삼키기 좋은 크기 — 코엔자임 정제의 캡슐 사이즈가 아담하고 매우 작아 목에 부드럽게 넘어감
+뛰어난 위장 유연성 — 복용 후 하복부에서 신물이나 미슥거리는 자극 없이 속 편하게 일상 유지가 됨</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 파인애플 맛 — 상큼달콤한 파인애플 사탕 맛으로 남녀노소 누구나 기분 좋게 챙겨 먹기 적합함
-하체 붓기 완화 효과 — 다리 부종 완화에 효과가 있어 저녁마다 다리가 무겁거나 쉽게 붓는 이들에게 유용함</t>
+          <t>체감되는 숙면 유도 — 복용 후 새벽에 뒤척이거나 갑자기 깨는 일 없이 안정감 있는 깊은 수면이 가능함
+부담 없는 장기 보충 — 일조량이 부족할 때 비타민D를 저렴하게 대량 구비하여 온 가족이 먹기에 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>복용이 손쉬운 필름 — 입천장이나 혀에 간편하게 부착하여 녹여 먹는 구강용 필름 제형이라 섭취가 매우 쉬움</t>
+          <t>간결한 일회 복용 — 번거롭게 수시로 먹을 필요 없이 하루 한 정만 간편하게 섭취해 관리가 쉬움
+한 달 단위 안심 보관 — 딱 한 달 동안 먹기 좋게 분량 조절이 되어 위생적으로 휴대하고 유지하기 편리함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>이중 배합의 건강 케어 — 장 건강을 위한 유산균 공급은 물론 식후 혈당 케어까지 캡슐 하나로 동시에 관리함
-부담 없는 저렴한 단가 — 매일 섭취해도 가격에 대한 지출 부담이 전혀 없으며 캡슐 타입이라 휴대에도 용이함</t>
+          <t>우수한 경비 조절 — 몸보신 아르기닌 입문용으로 고가의 세트 대비 부담 없는 비용으로 가볍게 활력을 즐김</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성 — 여행이나 출장 시 큰 영양제 통을 들고 다닐 필요 없이 필요 소량만 간편히 지참할 수 있음
-적은 비린내와 목넘김 — 오메가3 특유의 불쾌한 생선 냄새가 올라오지 않아 목넘김에 거부감이 적음</t>
+          <t>눈가 떨림 장애 해소 — 마그네슘 부족 현상인 눈가 안면 미세 떨림 증세를 신속하게 바로 잡아 줌
+신뢰 가는 성분 처방 — 전문 약사가 가볍게 복용하기 좋게 선별해 준 마그네슘이라 다이소 가격에 안심하고 섭취함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>아이들의 높은 선호도 — 달콤하고 맛있는 샐러드 미니볼 형태로, 약을 기피하는 어린아이들도 아주 좋아함
-복용의 우수한 편리성 — 한 포씩 소포장 설계되어 보관하기 유용하고 매일 아침 가볍게 뜯어 먹이기 편리함</t>
+          <t>질림 없는 콤팩트 — 큰 용량을 통째로 사서 보관하면 먹다 남기는 분들을 위해 실용적인 미니 소용량임
+우수한 소량 이동성 — 6일분의 납작하고 아담한 패키지로 출장이나 여행 시 짐 가방 공간을 덜 차지함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>신뢰성 높은 원료 구성 — 저렴한 단가이지만 소연골 유래 원료 기반의 콘드로이친을 채택하여 신뢰할 만함
-깔끔한 한 달 분량 포장 — 30일 단위로 콤팩트하게 개별 상자 포장되어 책상 위에 상시 구비해 두며 먹기 좋음</t>
+          <t>여성 이너 유산균 — 질 건강 이너케어 성분과 장 건강 유산균을 하나의 캡슐에 함축하여 무척 합리적임</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>가성비가 돋보이는 구성 — 가성비가 매우 뛰어나 매일 영양제를 장기적으로 챙겨 먹는 이들에게 유용함
-피부에 와닿는 체감 효과 — 꾸준히 지속적으로 복용할 경우 확실히 전보다 피부 건강과 탄력 회복에 도움을 줌</t>
+          <t>여성 전용 밸런스 — 여성 신체 리듬과 성분에 중점을 맞춘 기능 배합을 단 한 포로 해결할 수 있음
+위생적인 간소 섭취 — 외출 시 주머니에 낱개 수납하여 야외에서 가볍게 건강을 채우기 수월함</t>
         </is>
       </c>
     </row>
@@ -5470,31 +5956,31 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 정제 맛 — 입에 닿았을 때 느껴지는 특유의 맛이 별로여서 삼키기 부담스러운 단점이 있음</t>
+          <t>많은 정제 복용 횟수 — 일일 섭취 기준 충족을 위해 한 번에 3알씩 챙겨야 하므로 삼킬 때 누락되기 쉬움</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>빈번한 일시 품절 현상 — 매장이나 온라인 몰에서 자주 품절되어 재고가 부족해 제때 구매하기가 쉽지 않음</t>
+          <t>알약의 아쉬운 미각 — 정제를 삼키기 전 표면에서 다소 씁쓸하거나 나쁜 맛이 느껴져 삼키는 과정이 힘듦</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>개인에 따라 다른 맛 — 맛의 기호성에 차이가 있어 일부 이용자에게는 매우 맛이 없고 먹기 곤욕스럽게 느껴짐</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>과도하게 큰 캡슐 크기 — 알약 형태의 오메가3 캡슐 한 알의 크기가 제법 큰 편이어서 물과 삼키기 다소 벅참</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 개별 함량 — 1알로는 최적 함량을 채우기 다소 어려워 총 2정씩 꼬박꼬박 챙겨 먹어야 함</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>미약한 체력 각성 — 체감되는 즉각적인 에너지 대사나 신체 충전 효과를 기대하는 데에는 편차가 있음</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>극심한 배송 지연 발생 — 주문 처리가 매우 늦어 명절 전에 결제한 품목이 오랜 기간 지연 배송되는 현상이 발생함</t>
+          <t>서서히 나타나는 작용 — 복용 즉시 시원하거나 뚜렷한 신체 반응 변화를 명확히 체감하기에는 다소 더딤</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -5507,42 +5993,42 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>1,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -5640,7 +6126,1129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>이미지URL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>리뷰평점</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>리뷰건수</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>긍정1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>긍정2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>긍정3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>부정1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>부정2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>부정3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>미궁365 대장사랑 프리미엄 14포 (7일분)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>미궁365</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164353&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016435307ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>310</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[10/7 하루특가][단독기획/달바젤리] 비거너리 다이어트 젤리 4200mg 7포(+2포) (샤인머스캣맛) (9일분)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>비거너리바이달바</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000255305&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025530534ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17222</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>빠른 얼굴 붓기 제거 — 야식이나 자극적인 음주를 한 다음 날 자고 일어났을 때의 땡땡함 완화에 즉효가 있음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>삼키기 부드러운 환 — 아주 조그마한 미니미 크기로 동글동글하게 세공되어 목을 타고 부드럽게 잘 넘어감</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[올영단독] 닥터린 파비플로라 알파CD 프리미엄 10g X 30포 (1개월분)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>닥터린</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>17,060원</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236821&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023682102ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>559</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263899&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026389913ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>549</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>이너뷰티 단일 해결 — 한 포 섭취로 피부 탄력에 좋은 비타민C, 히알루론산, 글루타치온을 원스톱 충전함</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>새콤한 라임 풍미 — 상큼하고 산뜻한 레몬라임 베이스로 조율된 탄력 젤리 형태라 간식으로 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000002944&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0000/A00000000294414ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21769</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>확실한 피로 완화 — 매일 아침 섭취 시 찌뿌둥한 하루 컨디션이 올라가며 활력을 오랜 시간 유지해 줌</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>압도적 판매 가성비 — 고려은단 특유의 안전한 비타민 품질에 올리브영 세일가가 더해져 부담 없이 챙기기 좋음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>식도 부근 강한 산기 — 고함량 레벨이라 신맛의 여운이 입안 가득 매우 짙게 남아 위산 역류 등에 신경 쓰임</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61,900원</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41312</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>무너진 면역력 강화 — 일과 학습 등 극도의 과로로 떨어진 면역력을 신속하게 강화해 컨디션을 높여 줌</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>소장 욕구 채우는 굿즈 — 인기 포차코 캐릭터와 정식 협업하여 세련된 물빠짐 수영 파우치 등을 선사해 유용함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>다채로운 복용 방식 — 특유의 꾸덕하고 진한 액상을 탄산수나 생수에 타서 음료 에이드 형태로 가볍게 청량하게 섭취함</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>무시 못 할 지출 단가 — 비타민 에르메스라는 평판답게 매일 장기 복용을 고집하기에는 1병당 가격이 상당함</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>미궁365</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>비거너리바이달바</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>닥터린</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>미궁365 대장사랑 프리미엄 14포 (7일분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[10/7 하루특가][단독기획/달바젤리] 비거너리 다이어트 젤리 4200mg 7포(+2포) (샤인머스캣맛) (9일분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[올영단독] 닥터린 파비플로라 알파CD 프리미엄 10g X 30포 (1개월분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>평점</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>310</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="n">
+        <v>17222</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>559</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>549</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>21769</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>41312</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>긍정리뷰</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>빠른 얼굴 붓기 제거 — 야식이나 자극적인 음주를 한 다음 날 자고 일어났을 때의 땡땡함 완화에 즉효가 있음
+삼키기 부드러운 환 — 아주 조그마한 미니미 크기로 동글동글하게 세공되어 목을 타고 부드럽게 잘 넘어감</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰티 단일 해결 — 한 포 섭취로 피부 탄력에 좋은 비타민C, 히알루론산, 글루타치온을 원스톱 충전함
+새콤한 라임 풍미 — 상큼하고 산뜻한 레몬라임 베이스로 조율된 탄력 젤리 형태라 간식으로 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>확실한 피로 완화 — 매일 아침 섭취 시 찌뿌둥한 하루 컨디션이 올라가며 활력을 오랜 시간 유지해 줌
+압도적 판매 가성비 — 고려은단 특유의 안전한 비타민 품질에 올리브영 세일가가 더해져 부담 없이 챙기기 좋음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>무너진 면역력 강화 — 일과 학습 등 극도의 과로로 떨어진 면역력을 신속하게 강화해 컨디션을 높여 줌
+소장 욕구 채우는 굿즈 — 인기 포차코 캐릭터와 정식 협업하여 세련된 물빠짐 수영 파우치 등을 선사해 유용함
+다채로운 복용 방식 — 특유의 꾸덕하고 진한 액상을 탄산수나 생수에 타서 음료 에이드 형태로 가볍게 청량하게 섭취함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>부정리뷰</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>식도 부근 강한 산기 — 고함량 레벨이라 신맛의 여운이 입안 가득 매우 짙게 남아 위산 역류 등에 신경 쓰임</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>무시 못 할 지출 단가 — 비타민 에르메스라는 평판답게 매일 장기 복용을 고집하기에는 1병당 가격이 상당함</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>17,060원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>61,900원</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5669,24 +7277,32 @@
           <t>다이소몰</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -5696,10 +7312,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>23.3</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
@@ -5707,99 +7323,205 @@
       <c r="E3" t="n">
         <v>2</v>
       </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>23.3</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="F6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
